--- a/Automated_Pipeline/INPUT_EXCEL/DIS/DIS Theme 7 - Political Vulnerability.xlsx
+++ b/Automated_Pipeline/INPUT_EXCEL/DIS/DIS Theme 7 - Political Vulnerability.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin\Documents\GitHub\LB_DEV\Automated_Pipeline\INPUT_EXCEL\DIS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68BD5661-F5C9-49C8-A7A9-5D362CD9D936}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83C71599-287F-4EC2-943C-376166F361AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t>ADM2_Name</t>
   </si>
@@ -153,6 +153,9 @@
   </si>
   <si>
     <t>Municipal authorities effect on quality of life: worsened life somewhat + alot</t>
+  </si>
+  <si>
+    <t>Demographic Factor</t>
   </si>
 </sst>
 </file>
@@ -195,9 +198,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -478,25 +484,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M27"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:N27"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="22.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.5546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="21" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="52.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="53.28515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="68.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="52.44140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="53.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="68.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -536,8 +542,11 @@
       <c r="M1" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N1" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -577,8 +586,11 @@
       <c r="M2" s="1">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N2" s="2">
+        <v>1.1869461794629933E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -618,8 +630,11 @@
       <c r="M3" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N3" s="2">
+        <v>0.30995190416721602</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -659,8 +674,11 @@
       <c r="M4" s="1">
         <v>12.9</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N4" s="2">
+        <v>0.173487076178447</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -700,49 +718,55 @@
       <c r="M5" s="1">
         <v>4.3</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N5" s="2">
+        <v>1.8316439214481998E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B6">
         <v>37</v>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D6">
-        <v>89.3</v>
+        <v>87.7</v>
       </c>
       <c r="E6">
-        <v>30.7</v>
+        <v>10.8</v>
       </c>
       <c r="F6">
-        <v>29.5</v>
+        <v>92.7</v>
       </c>
       <c r="G6">
+        <v>7.6</v>
+      </c>
+      <c r="H6">
+        <v>88.6</v>
+      </c>
+      <c r="I6">
+        <v>7.9</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6" s="1">
+        <v>0</v>
+      </c>
+      <c r="L6" s="1">
         <v>7.1</v>
       </c>
-      <c r="H6">
-        <v>31.8</v>
-      </c>
-      <c r="I6">
-        <v>3.7</v>
-      </c>
-      <c r="J6">
-        <v>7</v>
-      </c>
-      <c r="K6" s="1">
-        <v>2.4</v>
-      </c>
-      <c r="L6" s="1">
-        <v>3.3</v>
-      </c>
       <c r="M6" s="1">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="N6" s="2">
+        <v>1.5402957389372401E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -782,8 +806,11 @@
       <c r="M7" s="1">
         <v>4.2</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N7" s="2">
+        <v>0.912994606868335</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -823,500 +850,539 @@
       <c r="M8" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N8" s="2">
+        <v>3.3397456120982998E-4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B9">
+        <v>45</v>
+      </c>
+      <c r="C9">
+        <v>12</v>
+      </c>
+      <c r="D9">
+        <v>91.9</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>24.9</v>
+      </c>
+      <c r="G9">
+        <v>43.1</v>
+      </c>
+      <c r="H9">
+        <v>6.4</v>
+      </c>
+      <c r="I9">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="J9">
+        <v>6</v>
+      </c>
+      <c r="K9" s="1">
+        <v>1.6</v>
+      </c>
+      <c r="L9" s="1">
+        <v>2.7</v>
+      </c>
+      <c r="M9" s="1">
+        <v>1.9</v>
+      </c>
+      <c r="N9" s="2">
+        <v>0.37288453784489001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10">
         <v>37</v>
       </c>
-      <c r="C9">
+      <c r="C10">
+        <v>3</v>
+      </c>
+      <c r="D10">
+        <v>89.3</v>
+      </c>
+      <c r="E10">
+        <v>30.7</v>
+      </c>
+      <c r="F10">
+        <v>29.5</v>
+      </c>
+      <c r="G10">
+        <v>7.1</v>
+      </c>
+      <c r="H10">
+        <v>31.8</v>
+      </c>
+      <c r="I10">
+        <v>3.7</v>
+      </c>
+      <c r="J10">
+        <v>7</v>
+      </c>
+      <c r="K10" s="1">
+        <v>2.4</v>
+      </c>
+      <c r="L10" s="1">
+        <v>3.3</v>
+      </c>
+      <c r="M10" s="1">
+        <v>0.9</v>
+      </c>
+      <c r="N10" s="2">
+        <v>4.9157750575908104E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11">
+        <v>48</v>
+      </c>
+      <c r="C11">
+        <v>5</v>
+      </c>
+      <c r="D11">
+        <v>95.3</v>
+      </c>
+      <c r="E11">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="F11">
+        <v>99</v>
+      </c>
+      <c r="G11">
+        <v>83.2</v>
+      </c>
+      <c r="H11">
+        <v>49.5</v>
+      </c>
+      <c r="I11">
+        <v>96.8</v>
+      </c>
+      <c r="J11">
+        <v>14</v>
+      </c>
+      <c r="K11" s="1">
+        <v>16.2</v>
+      </c>
+      <c r="L11" s="1">
+        <v>2</v>
+      </c>
+      <c r="M11" s="1">
+        <v>0</v>
+      </c>
+      <c r="N11" s="2">
+        <v>1.69538673036379E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12">
+        <v>37</v>
+      </c>
+      <c r="C12">
         <v>6</v>
       </c>
-      <c r="D9">
-        <v>87.7</v>
-      </c>
-      <c r="E9">
-        <v>10.8</v>
-      </c>
-      <c r="F9">
-        <v>92.7</v>
-      </c>
-      <c r="G9">
-        <v>7.6</v>
-      </c>
-      <c r="H9">
-        <v>88.6</v>
-      </c>
-      <c r="I9">
-        <v>7.9</v>
-      </c>
-      <c r="J9">
-        <v>1</v>
-      </c>
-      <c r="K9" s="1">
-        <v>0</v>
-      </c>
-      <c r="L9" s="1">
-        <v>7.1</v>
-      </c>
-      <c r="M9" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10">
-        <v>45</v>
-      </c>
-      <c r="C10">
-        <v>12</v>
-      </c>
-      <c r="D10">
-        <v>91.9</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>24.9</v>
-      </c>
-      <c r="G10">
-        <v>43.1</v>
-      </c>
-      <c r="H10">
-        <v>6.4</v>
-      </c>
-      <c r="I10">
-        <v>9.8000000000000007</v>
-      </c>
-      <c r="J10">
-        <v>6</v>
-      </c>
-      <c r="K10" s="1">
-        <v>1.6</v>
-      </c>
-      <c r="L10" s="1">
-        <v>2.7</v>
-      </c>
-      <c r="M10" s="1">
-        <v>1.9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11">
-        <v>34</v>
-      </c>
-      <c r="C11">
-        <v>3</v>
-      </c>
-      <c r="D11">
-        <v>89.800000000000011</v>
-      </c>
-      <c r="E11">
-        <v>12.7</v>
-      </c>
-      <c r="F11">
-        <v>100</v>
-      </c>
-      <c r="G11">
-        <v>54.3</v>
-      </c>
-      <c r="H11">
-        <v>83.8</v>
-      </c>
-      <c r="I11">
-        <v>30.2</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11" s="1">
-        <v>46.7</v>
-      </c>
-      <c r="L11" s="1">
-        <v>41.6</v>
-      </c>
-      <c r="M11" s="1">
-        <v>12.2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12">
-        <v>48</v>
-      </c>
-      <c r="C12">
+      <c r="D12">
+        <v>97.600000000000009</v>
+      </c>
+      <c r="E12">
+        <v>85.1</v>
+      </c>
+      <c r="F12">
+        <v>74</v>
+      </c>
+      <c r="G12">
+        <v>11.1</v>
+      </c>
+      <c r="H12">
+        <v>85.2</v>
+      </c>
+      <c r="I12">
+        <v>92.9</v>
+      </c>
+      <c r="J12">
         <v>5</v>
       </c>
-      <c r="D12">
-        <v>95.3</v>
-      </c>
-      <c r="E12">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="F12">
-        <v>99</v>
-      </c>
-      <c r="G12">
-        <v>83.2</v>
-      </c>
-      <c r="H12">
-        <v>49.5</v>
-      </c>
-      <c r="I12">
-        <v>96.8</v>
-      </c>
-      <c r="J12">
-        <v>14</v>
-      </c>
       <c r="K12" s="1">
-        <v>16.2</v>
+        <v>92</v>
       </c>
       <c r="L12" s="1">
-        <v>2</v>
+        <v>62.2</v>
       </c>
       <c r="M12" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+        <v>60.8</v>
+      </c>
+      <c r="N12" s="2">
+        <v>3.7238886931405701E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B13">
         <v>45</v>
       </c>
       <c r="C13">
+        <v>13</v>
+      </c>
+      <c r="D13">
+        <v>97.4</v>
+      </c>
+      <c r="E13">
+        <v>37.9</v>
+      </c>
+      <c r="F13">
+        <v>82.899999999999991</v>
+      </c>
+      <c r="G13">
+        <v>50.8</v>
+      </c>
+      <c r="H13">
+        <v>96.4</v>
+      </c>
+      <c r="I13">
+        <v>41</v>
+      </c>
+      <c r="J13">
+        <v>22</v>
+      </c>
+      <c r="K13" s="1">
+        <v>2.6</v>
+      </c>
+      <c r="L13" s="1">
+        <v>2.8</v>
+      </c>
+      <c r="M13" s="1">
+        <v>1.7</v>
+      </c>
+      <c r="N13" s="2">
+        <v>3.6042835012872698E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14">
+        <v>37</v>
+      </c>
+      <c r="C14">
+        <v>13</v>
+      </c>
+      <c r="D14">
+        <v>68.5</v>
+      </c>
+      <c r="E14">
+        <v>3.7</v>
+      </c>
+      <c r="F14">
+        <v>99.6</v>
+      </c>
+      <c r="G14">
+        <v>7.3999999999999995</v>
+      </c>
+      <c r="H14">
+        <v>7.9</v>
+      </c>
+      <c r="I14">
+        <v>0.7</v>
+      </c>
+      <c r="J14">
+        <v>35</v>
+      </c>
+      <c r="K14" s="1">
+        <v>0</v>
+      </c>
+      <c r="L14" s="1">
+        <v>0</v>
+      </c>
+      <c r="M14" s="1">
+        <v>0</v>
+      </c>
+      <c r="N14" s="2">
+        <v>1.1397852064198718E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15">
+        <v>34</v>
+      </c>
+      <c r="C15">
+        <v>16</v>
+      </c>
+      <c r="D15">
+        <v>59.8</v>
+      </c>
+      <c r="E15">
+        <v>46.9</v>
+      </c>
+      <c r="F15">
+        <v>98.100000000000009</v>
+      </c>
+      <c r="G15">
+        <v>14</v>
+      </c>
+      <c r="H15">
+        <v>82.8</v>
+      </c>
+      <c r="I15">
+        <v>42</v>
+      </c>
+      <c r="J15">
+        <v>18</v>
+      </c>
+      <c r="K15" s="1">
+        <v>9.5</v>
+      </c>
+      <c r="L15" s="1">
+        <v>52.4</v>
+      </c>
+      <c r="M15" s="1">
+        <v>4.8</v>
+      </c>
+      <c r="N15" s="2">
+        <v>1.7468626256874444E-3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>10</v>
+      </c>
+      <c r="B16">
+        <v>34</v>
+      </c>
+      <c r="C16">
+        <v>3</v>
+      </c>
+      <c r="D16">
+        <v>89.800000000000011</v>
+      </c>
+      <c r="E16">
+        <v>12.7</v>
+      </c>
+      <c r="F16">
+        <v>100</v>
+      </c>
+      <c r="G16">
+        <v>54.3</v>
+      </c>
+      <c r="H16">
+        <v>83.8</v>
+      </c>
+      <c r="I16">
+        <v>30.2</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16" s="1">
+        <v>46.7</v>
+      </c>
+      <c r="L16" s="1">
+        <v>41.6</v>
+      </c>
+      <c r="M16" s="1">
+        <v>12.2</v>
+      </c>
+      <c r="N16" s="2">
+        <v>4.2273928526297903E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>12</v>
+      </c>
+      <c r="B17">
+        <v>45</v>
+      </c>
+      <c r="C17">
         <v>6</v>
       </c>
-      <c r="D13">
+      <c r="D17">
         <v>88</v>
       </c>
-      <c r="E13">
+      <c r="E17">
         <v>29.4</v>
       </c>
-      <c r="F13">
+      <c r="F17">
         <v>81.599999999999994</v>
       </c>
-      <c r="G13">
+      <c r="G17">
         <v>6.2</v>
       </c>
-      <c r="H13">
+      <c r="H17">
         <v>75.5</v>
       </c>
-      <c r="I13">
+      <c r="I17">
         <v>15.3</v>
       </c>
-      <c r="J13">
+      <c r="J17">
         <v>11</v>
       </c>
-      <c r="K13" s="1">
-        <v>0</v>
-      </c>
-      <c r="L13" s="1">
+      <c r="K17" s="1">
+        <v>0</v>
+      </c>
+      <c r="L17" s="1">
         <v>3.3</v>
       </c>
-      <c r="M13" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="M17" s="1">
+        <v>0</v>
+      </c>
+      <c r="N17" s="2">
+        <v>0.108656326236893</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
         <v>13</v>
       </c>
-      <c r="B14">
+      <c r="B18">
         <v>40</v>
       </c>
-      <c r="C14">
+      <c r="C18">
         <v>16</v>
       </c>
-      <c r="D14">
+      <c r="D18">
         <v>28.700000000000003</v>
       </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-      <c r="F14">
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
         <v>54.1</v>
       </c>
-      <c r="G14">
+      <c r="G18">
         <v>13.4</v>
       </c>
-      <c r="H14">
+      <c r="H18">
         <v>43.3</v>
       </c>
-      <c r="I14">
+      <c r="I18">
         <v>47.1</v>
       </c>
-      <c r="J14">
+      <c r="J18">
         <v>8</v>
       </c>
-      <c r="K14" s="1">
+      <c r="K18" s="1">
         <v>29.1</v>
       </c>
-      <c r="L14" s="1">
+      <c r="L18" s="1">
         <v>29.6</v>
       </c>
-      <c r="M14" s="1">
+      <c r="M18" s="1">
         <v>22.6</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="N18" s="2">
+        <v>0.11772725577675899</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
         <v>14</v>
       </c>
-      <c r="B15">
+      <c r="B19">
         <v>45</v>
       </c>
-      <c r="C15">
+      <c r="C19">
         <v>12</v>
       </c>
-      <c r="D15">
+      <c r="D19">
         <v>95.3</v>
       </c>
-      <c r="E15">
+      <c r="E19">
         <v>86.1</v>
       </c>
-      <c r="F15">
+      <c r="F19">
         <v>59.4</v>
       </c>
-      <c r="G15">
+      <c r="G19">
         <v>28.5</v>
       </c>
-      <c r="H15">
+      <c r="H19">
         <v>78.7</v>
       </c>
-      <c r="I15">
+      <c r="I19">
         <v>86.3</v>
       </c>
-      <c r="J15">
+      <c r="J19">
         <v>33</v>
       </c>
-      <c r="K15" s="1">
+      <c r="K19" s="1">
         <v>67.400000000000006</v>
       </c>
-      <c r="L15" s="1">
+      <c r="L19" s="1">
         <v>52.8</v>
       </c>
-      <c r="M15" s="1">
+      <c r="M19" s="1">
         <v>38.299999999999997</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16">
-        <v>37</v>
-      </c>
-      <c r="C16">
-        <v>6</v>
-      </c>
-      <c r="D16">
-        <v>97.600000000000009</v>
-      </c>
-      <c r="E16">
-        <v>85.1</v>
-      </c>
-      <c r="F16">
-        <v>74</v>
-      </c>
-      <c r="G16">
-        <v>11.1</v>
-      </c>
-      <c r="H16">
-        <v>85.2</v>
-      </c>
-      <c r="I16">
-        <v>92.9</v>
-      </c>
-      <c r="J16">
-        <v>5</v>
-      </c>
-      <c r="K16" s="1">
-        <v>92</v>
-      </c>
-      <c r="L16" s="1">
-        <v>62.2</v>
-      </c>
-      <c r="M16" s="1">
-        <v>60.8</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="N19" s="2">
+        <v>5.1722780863039199E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
         <v>16</v>
-      </c>
-      <c r="B17">
-        <v>34</v>
-      </c>
-      <c r="C17">
-        <v>13</v>
-      </c>
-      <c r="D17">
-        <v>11.7</v>
-      </c>
-      <c r="E17">
-        <v>12.9</v>
-      </c>
-      <c r="F17">
-        <v>24.6</v>
-      </c>
-      <c r="G17">
-        <v>4.3</v>
-      </c>
-      <c r="H17">
-        <v>10.1</v>
-      </c>
-      <c r="I17">
-        <v>0</v>
-      </c>
-      <c r="J17">
-        <v>5</v>
-      </c>
-      <c r="K17" s="1">
-        <v>0</v>
-      </c>
-      <c r="L17" s="1">
-        <v>0</v>
-      </c>
-      <c r="M17" s="1">
-        <v>10.8</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>17</v>
-      </c>
-      <c r="B18">
-        <v>45</v>
-      </c>
-      <c r="C18">
-        <v>13</v>
-      </c>
-      <c r="D18">
-        <v>97.4</v>
-      </c>
-      <c r="E18">
-        <v>37.9</v>
-      </c>
-      <c r="F18">
-        <v>82.899999999999991</v>
-      </c>
-      <c r="G18">
-        <v>50.8</v>
-      </c>
-      <c r="H18">
-        <v>96.4</v>
-      </c>
-      <c r="I18">
-        <v>41</v>
-      </c>
-      <c r="J18">
-        <v>22</v>
-      </c>
-      <c r="K18" s="1">
-        <v>2.6</v>
-      </c>
-      <c r="L18" s="1">
-        <v>2.8</v>
-      </c>
-      <c r="M18" s="1">
-        <v>1.7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>18</v>
-      </c>
-      <c r="B19">
-        <v>37</v>
-      </c>
-      <c r="C19">
-        <v>13</v>
-      </c>
-      <c r="D19">
-        <v>68.5</v>
-      </c>
-      <c r="E19">
-        <v>3.7</v>
-      </c>
-      <c r="F19">
-        <v>99.6</v>
-      </c>
-      <c r="G19">
-        <v>7.3999999999999995</v>
-      </c>
-      <c r="H19">
-        <v>7.9</v>
-      </c>
-      <c r="I19">
-        <v>0.7</v>
-      </c>
-      <c r="J19">
-        <v>35</v>
-      </c>
-      <c r="K19" s="1">
-        <v>0</v>
-      </c>
-      <c r="L19" s="1">
-        <v>0</v>
-      </c>
-      <c r="M19" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>19</v>
       </c>
       <c r="B20">
         <v>34</v>
       </c>
       <c r="C20">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D20">
-        <v>59.8</v>
+        <v>11.7</v>
       </c>
       <c r="E20">
-        <v>46.9</v>
+        <v>12.9</v>
       </c>
       <c r="F20">
-        <v>98.100000000000009</v>
+        <v>24.6</v>
       </c>
       <c r="G20">
-        <v>14</v>
+        <v>4.3</v>
       </c>
       <c r="H20">
-        <v>82.8</v>
+        <v>10.1</v>
       </c>
       <c r="I20">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="J20">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="K20" s="1">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="L20" s="1">
-        <v>52.4</v>
+        <v>0</v>
       </c>
       <c r="M20" s="1">
-        <v>4.8</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+        <v>10.8</v>
+      </c>
+      <c r="N20" s="2">
+        <v>1.3293990966245801E-3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -1356,8 +1422,11 @@
       <c r="M21" s="1">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N21" s="2">
+        <v>3.5058390756103106E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>21</v>
       </c>
@@ -1397,90 +1466,99 @@
       <c r="M22" s="1">
         <v>5.0999999999999996</v>
       </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N22" s="2">
+        <v>0.32918962703122273</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23">
+        <v>40</v>
+      </c>
+      <c r="C23">
+        <v>42</v>
+      </c>
+      <c r="D23">
+        <v>35.900000000000006</v>
+      </c>
+      <c r="E23">
+        <v>7.5</v>
+      </c>
+      <c r="F23">
+        <v>52.3</v>
+      </c>
+      <c r="G23">
+        <v>11.5</v>
+      </c>
+      <c r="H23">
+        <v>26.6</v>
+      </c>
+      <c r="I23">
+        <v>62.1</v>
+      </c>
+      <c r="J23">
+        <v>40</v>
+      </c>
+      <c r="K23" s="1">
+        <v>1.9</v>
+      </c>
+      <c r="L23" s="1">
+        <v>1.9</v>
+      </c>
+      <c r="M23" s="1">
+        <v>1.8</v>
+      </c>
+      <c r="N23" s="2">
+        <v>3.0815220119826084E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
         <v>22</v>
       </c>
-      <c r="B23">
+      <c r="B24">
         <v>37</v>
       </c>
-      <c r="C23">
-        <v>0</v>
-      </c>
-      <c r="D23">
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24">
         <v>44</v>
       </c>
-      <c r="E23">
+      <c r="E24">
         <v>11.3</v>
       </c>
-      <c r="F23">
+      <c r="F24">
         <v>59.3</v>
       </c>
-      <c r="G23">
+      <c r="G24">
         <v>18.600000000000001</v>
       </c>
-      <c r="H23">
+      <c r="H24">
         <v>14.8</v>
       </c>
-      <c r="I23">
+      <c r="I24">
         <v>10.199999999999999</v>
       </c>
-      <c r="J23">
+      <c r="J24">
         <v>235</v>
       </c>
-      <c r="K23" s="1">
+      <c r="K24" s="1">
         <v>4.5999999999999996</v>
       </c>
-      <c r="L23" s="1">
+      <c r="L24" s="1">
         <v>4</v>
       </c>
-      <c r="M23" s="1">
+      <c r="M24" s="1">
         <v>4.4000000000000004</v>
       </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>23</v>
-      </c>
-      <c r="B24">
-        <v>40</v>
-      </c>
-      <c r="C24">
-        <v>42</v>
-      </c>
-      <c r="D24">
-        <v>35.900000000000006</v>
-      </c>
-      <c r="E24">
-        <v>7.5</v>
-      </c>
-      <c r="F24">
-        <v>52.3</v>
-      </c>
-      <c r="G24">
-        <v>11.5</v>
-      </c>
-      <c r="H24">
-        <v>26.6</v>
-      </c>
-      <c r="I24">
-        <v>62.1</v>
-      </c>
-      <c r="J24">
-        <v>40</v>
-      </c>
-      <c r="K24" s="1">
-        <v>1.9</v>
-      </c>
-      <c r="L24" s="1">
-        <v>1.9</v>
-      </c>
-      <c r="M24" s="1">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N24" s="2">
+        <v>1.111433700233082E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>24</v>
       </c>
@@ -1520,8 +1598,11 @@
       <c r="M25" s="1">
         <v>1.2</v>
       </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N25" s="2">
+        <v>8.0607279199497103E-3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>25</v>
       </c>
@@ -1561,8 +1642,11 @@
       <c r="M26" s="1">
         <v>0.9</v>
       </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N26" s="2">
+        <v>1.8816869601642881E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>26</v>
       </c>
@@ -1602,8 +1686,14 @@
       <c r="M27" s="1">
         <v>8.1</v>
       </c>
+      <c r="N27" s="2">
+        <v>6.4208322080505933E-2</v>
+      </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M27">
+    <sortCondition ref="A1:A27"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>